--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/OREGON_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/OREGON_2020.xlsx
@@ -913,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="D31">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="32">
@@ -1147,7 +1147,7 @@
         <v>4</v>
       </c>
       <c r="D44">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="45">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C53">
@@ -1543,7 +1543,7 @@
         <v>4</v>
       </c>
       <c r="D66">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="67">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C96">
@@ -2317,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="D109">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="110">
@@ -2551,7 +2551,7 @@
         <v>4</v>
       </c>
       <c r="D122">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="123">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C135">
@@ -2803,7 +2803,7 @@
         <v>4</v>
       </c>
       <c r="D136">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="137">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C146">
@@ -3217,7 +3217,7 @@
         <v>4</v>
       </c>
       <c r="D159">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="160">
@@ -3523,7 +3523,7 @@
         <v>4</v>
       </c>
       <c r="D176">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="177">
@@ -3775,7 +3775,7 @@
         <v>4</v>
       </c>
       <c r="D190">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="191">
@@ -4009,7 +4009,7 @@
         <v>4</v>
       </c>
       <c r="D203">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="204">
@@ -4027,7 +4027,7 @@
         <v>4</v>
       </c>
       <c r="D204">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="205">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C211">
@@ -4657,7 +4657,7 @@
         <v>4</v>
       </c>
       <c r="D239">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="240">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C244">
@@ -4765,7 +4765,7 @@
         <v>4</v>
       </c>
       <c r="D245">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="246">
@@ -4801,7 +4801,7 @@
         <v>4</v>
       </c>
       <c r="D247">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="248">
@@ -5125,7 +5125,7 @@
         <v>4</v>
       </c>
       <c r="D265">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="266">
@@ -5629,7 +5629,7 @@
         <v>4</v>
       </c>
       <c r="D293">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="294">
@@ -5701,7 +5701,7 @@
         <v>4</v>
       </c>
       <c r="D297">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="298">
@@ -6007,7 +6007,7 @@
         <v>4</v>
       </c>
       <c r="D314">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="315">
@@ -6061,7 +6061,7 @@
         <v>4</v>
       </c>
       <c r="D317">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="318">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C322">
@@ -6295,7 +6295,7 @@
         <v>4</v>
       </c>
       <c r="D330">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="331">
@@ -7177,7 +7177,7 @@
         <v>4</v>
       </c>
       <c r="D379">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="380">
@@ -7195,7 +7195,7 @@
         <v>4</v>
       </c>
       <c r="D380">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="381">
@@ -7213,7 +7213,7 @@
         <v>4</v>
       </c>
       <c r="D381">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="382">
@@ -7735,7 +7735,7 @@
         <v>4</v>
       </c>
       <c r="D410">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="411">
@@ -7843,7 +7843,7 @@
         <v>4</v>
       </c>
       <c r="D416">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="417">
@@ -7861,7 +7861,7 @@
         <v>4</v>
       </c>
       <c r="D417">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="418">
@@ -8293,7 +8293,7 @@
         <v>4</v>
       </c>
       <c r="D441">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="442">
@@ -8455,7 +8455,7 @@
         <v>4</v>
       </c>
       <c r="D450">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="451">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C469">
@@ -8869,7 +8869,7 @@
         <v>4</v>
       </c>
       <c r="D473">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="474">
@@ -8959,7 +8959,7 @@
         <v>4</v>
       </c>
       <c r="D478">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="479">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C482">
@@ -9247,7 +9247,7 @@
         <v>4</v>
       </c>
       <c r="D494">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="495">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C505">
@@ -9481,7 +9481,7 @@
         <v>4</v>
       </c>
       <c r="D507">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="508">
@@ -9798,14 +9798,14 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C525">
         <v>4</v>
       </c>
       <c r="D525">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="526">
@@ -9823,7 +9823,7 @@
         <v>4</v>
       </c>
       <c r="D526">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="527">
@@ -9859,7 +9859,7 @@
         <v>4</v>
       </c>
       <c r="D528">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="529">
@@ -9913,7 +9913,7 @@
         <v>4</v>
       </c>
       <c r="D531">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="532">
@@ -10003,7 +10003,7 @@
         <v>4</v>
       </c>
       <c r="D536">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="537">
@@ -10921,7 +10921,7 @@
         <v>4</v>
       </c>
       <c r="D587">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="588">
@@ -11029,7 +11029,7 @@
         <v>4</v>
       </c>
       <c r="D593">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="594">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C641">
@@ -12073,7 +12073,7 @@
         <v>4</v>
       </c>
       <c r="D651">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="652">
@@ -12469,7 +12469,7 @@
         <v>4</v>
       </c>
       <c r="D673">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="674">
@@ -12577,7 +12577,7 @@
         <v>4</v>
       </c>
       <c r="D679">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="680">
@@ -12865,7 +12865,7 @@
         <v>4</v>
       </c>
       <c r="D695">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="696">
@@ -13369,7 +13369,7 @@
         <v>4</v>
       </c>
       <c r="D723">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="724">
@@ -13585,7 +13585,7 @@
         <v>4</v>
       </c>
       <c r="D735">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="736">
@@ -13837,7 +13837,7 @@
         <v>4</v>
       </c>
       <c r="D749">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="750">
@@ -13873,7 +13873,7 @@
         <v>4</v>
       </c>
       <c r="D751">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="752">
@@ -13927,7 +13927,7 @@
         <v>4</v>
       </c>
       <c r="D754">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="755">
@@ -14161,7 +14161,7 @@
         <v>4</v>
       </c>
       <c r="D767">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="768">
@@ -14737,7 +14737,7 @@
         <v>4</v>
       </c>
       <c r="D799">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="800">
@@ -14971,7 +14971,7 @@
         <v>4</v>
       </c>
       <c r="D812">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="813">
@@ -15601,7 +15601,7 @@
         <v>4</v>
       </c>
       <c r="D847">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="848">
@@ -15619,7 +15619,7 @@
         <v>4</v>
       </c>
       <c r="D848">
-        <v>0.0009732360097323601</v>
+        <v>0.00097323600973236</v>
       </c>
     </row>
     <row r="849">
